--- a/excel-campeonatos.xlsx
+++ b/excel-campeonatos.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\deportazo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:10000001_{F8FD9647-9647-445E-B279-0DA3B67AF978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6429F56D-3F4B-4DDA-BD23-CC7EED23A96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6AAC4C82-243A-49E8-898B-368379F134C3}"/>
   </bookViews>
   <sheets>
     <sheet name="SORTEO CORAZÓN LATINO V" sheetId="1" r:id="rId1"/>
+    <sheet name="LISTA" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="72">
   <si>
     <t>EQUIPO1</t>
   </si>
@@ -102,9 +102,6 @@
     <t>DUDU</t>
   </si>
   <si>
-    <t>SORTEO CORAZÓN LATINO VI- EQUIPOS</t>
-  </si>
-  <si>
     <t>NUEVOS</t>
   </si>
   <si>
@@ -186,12 +183,6 @@
     <t>SUSAN</t>
   </si>
   <si>
-    <t>MIEMBRO</t>
-  </si>
-  <si>
-    <t>POSICION</t>
-  </si>
-  <si>
     <t>EQUIPO5</t>
   </si>
   <si>
@@ -204,24 +195,9 @@
     <t>EQUIPO8</t>
   </si>
   <si>
-    <t>ATAQUE</t>
-  </si>
-  <si>
-    <t>ARMADO</t>
-  </si>
-  <si>
-    <t>LIBERO</t>
-  </si>
-  <si>
-    <t>ZAGUERO</t>
-  </si>
-  <si>
     <t>ZERGY</t>
   </si>
   <si>
-    <t>RECEPTOR</t>
-  </si>
-  <si>
     <t>LUIS</t>
   </si>
   <si>
@@ -229,13 +205,61 @@
   </si>
   <si>
     <t>SORTEO CORAZÓN LATINO -FIN DE AÑO- EQUIPOS</t>
+  </si>
+  <si>
+    <t>SORTEO CORAZÓN LATINO -FIN DE AÑO - EQUIPOS</t>
+  </si>
+  <si>
+    <t>MIEMBROS</t>
+  </si>
+  <si>
+    <t>RONALD</t>
+  </si>
+  <si>
+    <t>FRANCO2</t>
+  </si>
+  <si>
+    <t>HUGO</t>
+  </si>
+  <si>
+    <t>LEO</t>
+  </si>
+  <si>
+    <t>CONFIRMADOS</t>
+  </si>
+  <si>
+    <t>INVITADOS</t>
+  </si>
+  <si>
+    <t>MARCELO</t>
+  </si>
+  <si>
+    <t>GRIS</t>
+  </si>
+  <si>
+    <t>ROJO</t>
+  </si>
+  <si>
+    <t>ANDER</t>
+  </si>
+  <si>
+    <t>VERDE</t>
+  </si>
+  <si>
+    <t>NEGRO</t>
+  </si>
+  <si>
+    <t>BLANCO</t>
+  </si>
+  <si>
+    <t>AZUL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -294,23 +318,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="16"/>
+      <b/>
+      <sz val="36"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -329,8 +345,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="25">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -476,6 +498,93 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -483,8 +592,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
-      <right style="medium">
+      <right style="thin">
         <color theme="1"/>
       </right>
       <top/>
@@ -493,33 +615,91 @@
     </border>
     <border>
       <left style="medium">
-        <color theme="1"/>
+        <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color theme="1"/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
+      <bottom style="thick">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color theme="1"/>
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
       <right/>
       <top/>
@@ -527,102 +707,9 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -632,23 +719,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -656,121 +737,136 @@
     <xf numFmtId="1" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -802,23 +898,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>282677</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>153269</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1254781</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>375307</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1040181</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>93715</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>107813</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>36299</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 2">
+        <xdr:cNvPr id="4" name="Imagen 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92C515D5-1438-03C2-7C0E-F393E0DD8D6E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C33A011-6F5E-438F-4646-AFD0BE0573FF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -827,7 +923,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -840,8 +936,58 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6894871" y="6236979"/>
-          <a:ext cx="2551891" cy="2673506"/>
+          <a:off x="1673881" y="8795407"/>
+          <a:ext cx="2320132" cy="2251792"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>301381</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>251654</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>961035</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>109442</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8672B616-3CD7-4DE2-83FA-0CB5DF17A8C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6035119" y="2487687"/>
+          <a:ext cx="2470965" cy="2506050"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -876,25 +1022,25 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>232920</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>210207</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>195909</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>269158</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1137490</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>228214</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="2471174" cy="2467283"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Imagen 3">
+        <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C33A011-6F5E-438F-4646-AFD0BE0573FF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6024C36-5B3A-45A0-BA06-1B3BE719D71D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -903,7 +1049,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -916,58 +1062,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2702851" y="9235966"/>
-          <a:ext cx="2323467" cy="2238317"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>378789</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>688258</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1046563</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>107541</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Imagen 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D78DA70-5160-4450-4AC7-2156AC34B083}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6990983" y="688258"/>
-          <a:ext cx="2462161" cy="2556388"/>
+          <a:off x="10513389" y="269158"/>
+          <a:ext cx="2471174" cy="2467283"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -1001,7 +1097,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1322,650 +1418,898 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F0F3C9C-41F7-41C6-802A-201A8A1CCF1E}">
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" customWidth="1"/>
-    <col min="6" max="6" width="9.21875" customWidth="1"/>
-    <col min="7" max="7" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.44140625" customWidth="1"/>
-    <col min="9" max="9" width="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="17.109375" customWidth="1"/>
-    <col min="14" max="20" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="9.21875" customWidth="1"/>
+    <col min="8" max="8" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.44140625" customWidth="1"/>
+    <col min="10" max="10" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="29" customWidth="1"/>
+    <col min="17" max="20" width="17.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="60.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31"/>
-    </row>
-    <row r="2" spans="1:17" ht="29.4" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="36"/>
-      <c r="E2" s="13"/>
-      <c r="I2" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="J2" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="L2" s="24" t="s">
+    <row r="1" spans="1:16" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="12"/>
+    </row>
+    <row r="2" spans="1:16" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="37"/>
+    </row>
+    <row r="3" spans="1:16" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="M2" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="N2" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="O2" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="P2" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q2" s="24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="12">
-        <v>1</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="6">
+      <c r="B3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="3">
         <v>18</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="13"/>
-      <c r="I3" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-    </row>
-    <row r="4" spans="1:17" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="14">
+      <c r="D3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="8">
+        <v>35</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="2">
         <f>A3+1</f>
         <v>2</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="B4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="2">
         <f>C3+1</f>
         <v>19</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="13"/>
-      <c r="I4" s="2" t="s">
+      <c r="E4" s="8">
+        <f>E3+1</f>
+        <v>36</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="2">
+        <f t="shared" ref="A5:C19" si="0">A4+1</f>
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="8">
+        <f t="shared" ref="E5:E14" si="1">E4+1</f>
+        <v>37</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="2">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="8">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-    </row>
-    <row r="5" spans="1:17" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A5" s="14">
-        <f t="shared" ref="A5:C18" si="0">A4+1</f>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="35"/>
+    </row>
+    <row r="7" spans="1:16" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="2">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="8">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="L7" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="M7" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="N7" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="O7" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="P7" s="29" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="29.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A8" s="2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="8">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" s="23">
+        <v>1</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="L8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="5">
-        <f t="shared" si="0"/>
+      <c r="M8" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="N8" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A9" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="8">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="24">
+        <v>2</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="N9" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A10" s="2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="2">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="8">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="24">
+        <v>3</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="M10" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="N10" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A11" s="2">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="2">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="16">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11" s="24">
+        <v>4</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="M11" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="N11" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A12" s="2">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="13"/>
-      <c r="I5" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-    </row>
-    <row r="6" spans="1:17" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="14">
-        <f t="shared" si="0"/>
+      <c r="C12" s="2">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="17">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J12" s="24">
+        <v>5</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="M12" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="N12" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="2">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="2">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="19">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J13" s="24">
+        <v>6</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="N13" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A14" s="2">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="2">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="19">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J14" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="5">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="D6" s="8" t="s">
+      <c r="K14" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="L14" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="M14" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="N14" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="O14" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="P14" s="32" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="2">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="2">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="37"/>
+    </row>
+    <row r="16" spans="1:16" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="2">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="2">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="2">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="2">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="13"/>
-      <c r="I6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="22"/>
-      <c r="Q6" s="22"/>
-    </row>
-    <row r="7" spans="1:17" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="14">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="5">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="13"/>
-      <c r="I7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="22"/>
-    </row>
-    <row r="8" spans="1:17" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="14">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B8" s="8" t="s">
+      <c r="E17" s="8">
+        <f t="shared" ref="E17:E19" si="2">E16+1</f>
+        <v>2</v>
+      </c>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="2">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C8" s="5">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="13"/>
-      <c r="I8" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="42"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42"/>
-      <c r="N8" s="42"/>
-      <c r="O8" s="42"/>
-      <c r="P8" s="42"/>
-      <c r="Q8" s="42"/>
-    </row>
-    <row r="9" spans="1:17" ht="29.4" thickTop="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="14">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="5">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="13"/>
-    </row>
-    <row r="10" spans="1:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="14">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="5">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="13"/>
-    </row>
-    <row r="11" spans="1:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="14">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B11" s="8" t="s">
+      <c r="B18" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="20">
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C11" s="5">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="13"/>
-    </row>
-    <row r="12" spans="1:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="14">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="5">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="13"/>
-    </row>
-    <row r="13" spans="1:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="14">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="5">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="13"/>
-      <c r="J13" s="38"/>
-    </row>
-    <row r="14" spans="1:17" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="14">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="5">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="13"/>
-    </row>
-    <row r="15" spans="1:17" ht="29.4" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="14">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="5">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="13"/>
-    </row>
-    <row r="16" spans="1:17" ht="29.4" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A16" s="14">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="5">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="13"/>
-      <c r="I16" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="34"/>
-    </row>
-    <row r="17" spans="1:13" ht="29.4" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A17" s="14">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="5">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="13"/>
-      <c r="I17" s="40" t="s">
+      <c r="D18" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="J17" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="K17" s="24" t="s">
+      <c r="E18" s="8">
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="L17" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="M17" s="24" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A18" s="14">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="5">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" s="13"/>
-      <c r="I18" s="23">
-        <v>1</v>
-      </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="39"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="1:13" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A19" s="5">
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="2">
         <f>A18+1</f>
         <v>17</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="15"/>
-      <c r="I19" s="1">
-        <v>2</v>
-      </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="1:13" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A20" s="16"/>
-      <c r="E20" s="17"/>
-      <c r="I20" s="1">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="1:13" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A21" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="45" t="s">
+      <c r="B19" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E21" s="45"/>
-      <c r="I21" s="1">
+      <c r="C19" s="2">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="8">
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="1:13" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="14">
-        <v>34</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="27">
-        <v>42</v>
-      </c>
-      <c r="E22" s="28"/>
-      <c r="I22" s="1">
-        <v>5</v>
-      </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="1:13" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A23" s="14">
-        <f>A22+1</f>
-        <v>35</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="27"/>
-      <c r="E23" s="28"/>
-      <c r="I23" s="1">
-        <v>6</v>
-      </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="1:13" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A24" s="14">
-        <f t="shared" ref="A24:A30" si="1">A23+1</f>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="15"/>
+      <c r="F20" s="18"/>
+    </row>
+    <row r="21" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="49"/>
+      <c r="F21" s="50"/>
+    </row>
+    <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="54">
+        <f>MAX(A3:A19,C3:C19,E3:E19)</f>
+        <v>46</v>
+      </c>
+      <c r="B22" s="55"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="51">
+        <f>COUNTA(K8:P13)</f>
         <v>36</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="46"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="48"/>
-      <c r="I24" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="43"/>
-      <c r="K24" s="43"/>
-      <c r="L24" s="43"/>
-      <c r="M24" s="43"/>
-    </row>
-    <row r="25" spans="1:13" ht="29.4" thickTop="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="14">
-        <f t="shared" si="1"/>
-        <v>37</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48"/>
-    </row>
-    <row r="26" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="14">
-        <f t="shared" si="1"/>
-        <v>38</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="46"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
-    </row>
-    <row r="27" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="14">
-        <f t="shared" si="1"/>
-        <v>39</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="46"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-    </row>
-    <row r="28" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="14">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="46"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="48"/>
-    </row>
-    <row r="29" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="14">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C29" s="46"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="48"/>
-    </row>
-    <row r="30" spans="1:13" ht="29.4" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A30" s="19">
-        <f t="shared" si="1"/>
-        <v>42</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30" s="47"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="48"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="52"/>
+    </row>
+    <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="56"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="52"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="43"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="45"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="43"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="45"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="43"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="45"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="43"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="45"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="43"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="45"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="43"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="45"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="43"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="45"/>
+    </row>
+    <row r="31" spans="1:6" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="46"/>
+      <c r="B31" s="47"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="48"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="D24:E30"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E23"/>
-    <mergeCell ref="I1:Q1"/>
-    <mergeCell ref="I16:M16"/>
+  <mergeCells count="10">
+    <mergeCell ref="J6:P6"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A24:F31"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F23"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C23"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="B5:E23 B3:D4 E1:E4 B25:C30 B24:D24">
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>COUNTIF($J$18:$M$24,B1)&gt;0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4">
-      <formula>COUNTIF($J$3:$Q$8,B1)&gt;0</formula>
+  <conditionalFormatting sqref="E2 F3:F14 B3:D19 E15 F16:F19 B20:F20 A21:A22 A24 C32">
+    <cfRule type="expression" dxfId="1" priority="13">
+      <formula>COUNTIF($K$8:$P$14,A2)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="14" id="{00000000-000E-0000-0000-000004000000}">
+            <xm:f>COUNTIF(LISTA!$B$3:$I$9,A2)&gt;0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="3" tint="0.499984740745262"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>E2 F3:F14 B3:D19 E15 F16:F19 B20:F20 A21:A22 A24 C32</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32EEC62B-1BAF-4A76-96B8-B552F16D995C}">
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="9" width="17.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="57" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="59"/>
+    </row>
+    <row r="2" spans="1:9" ht="29.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A2" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="11">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+    </row>
+    <row r="4" spans="1:9" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+    </row>
+    <row r="5" spans="1:9" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+    </row>
+    <row r="6" spans="1:9" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+    </row>
+    <row r="7" spans="1:9" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+    </row>
+    <row r="8" spans="1:9" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+    </row>
+    <row r="9" spans="1:9" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+    </row>
+    <row r="10" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
